--- a/Proyecto Interno/Revisión de literatura/revistas.xlsx
+++ b/Proyecto Interno/Revisión de literatura/revistas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/Revisión de literatura/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{0066DE80-6092-42E6-82A4-1E674B457D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4CFFBF7-41BD-4A51-8B34-06EC948D0C4A}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{0066DE80-6092-42E6-82A4-1E674B457D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D43175E5-0BA3-4C98-8BAD-4E1EC13373B8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFA12644-6DEA-4385-99C0-446842811765}"/>
+    <workbookView minimized="1" xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" xr2:uid="{BFA12644-6DEA-4385-99C0-446842811765}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -320,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,6 +330,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,7 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -430,17 +436,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -457,10 +470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -850,7 +859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -906,59 +915,59 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:18" s="16" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="12">
         <v>5</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="6"/>
+      <c r="R3" s="12"/>
     </row>
     <row r="4" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -1017,10 +1026,10 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1076,7 +1085,7 @@
       <c r="A6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1129,64 +1138,64 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
